--- a/src/test/resources/venueAddressValues.xlsx
+++ b/src/test/resources/venueAddressValues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10314"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jamesturnbull/code/hmcts/ecm/ethos-repl-docmosis-service/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harpreet.jhita/IdeaProjects/ethos-repl-docmosis-service/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B39E46-F7FC-3C46-9687-D12B605FA113}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3879AAA2-555E-5346-84B1-6FDAE12D6441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="1740" windowWidth="30940" windowHeight="16900" xr2:uid="{57ECFE3E-99BE-FC40-B6CA-F6152164B97B}"/>
+    <workbookView xWindow="2840" yWindow="1740" windowWidth="30940" windowHeight="16900" activeTab="2" xr2:uid="{57ECFE3E-99BE-FC40-B6CA-F6152164B97B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bristol" sheetId="3" r:id="rId1"/>
@@ -632,9 +632,6 @@
     <t>1st Floor, Ashford House, County Square Shopping Centre, Ashford, TN23 1YB</t>
   </si>
   <si>
-    <t>Victory House, 30-34 Kingsway, London, WC2B 6EX</t>
-  </si>
-  <si>
     <t>London (Central), 4th Floor Fox Court, 30 Brooke Street, London, EC1N 7RS</t>
   </si>
   <si>
@@ -955,6 +952,9 @@
   </si>
   <si>
     <t>Teesside Justice Centre, Victoria Square, Middlesbrough, Cleveland, TS1 2AS</t>
+  </si>
+  <si>
+    <t>7 Newgate Street, London, EC1A 7AZ</t>
   </si>
 </sst>
 </file>
@@ -1043,11 +1043,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1055,15 +1054,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1084,9 +1079,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1124,7 +1119,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1230,7 +1225,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1372,7 +1367,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1397,10 +1392,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1731,184 +1726,184 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B5" s="12" t="s">
+      <c r="B8" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="12" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="B17" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="12" t="s">
+      <c r="B18" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="B19" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="B20" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1939,18 +1934,18 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1959,7 +1954,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1991,7 +1986,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2007,7 +2002,7 @@
         <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2015,7 +2010,7 @@
         <v>113</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2039,7 +2034,7 @@
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2071,7 +2066,7 @@
         <v>120</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2159,7 +2154,7 @@
         <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2215,7 +2210,7 @@
         <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2231,7 +2226,7 @@
         <v>140</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2263,7 +2258,7 @@
         <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2319,7 +2314,7 @@
         <v>151</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2327,7 +2322,7 @@
         <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2335,7 +2330,7 @@
         <v>153</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2375,7 +2370,7 @@
         <v>158</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2391,7 +2386,7 @@
         <v>160</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2423,7 +2418,7 @@
         <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2431,7 +2426,7 @@
         <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2447,23 +2442,23 @@
         <v>167</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2491,115 +2486,115 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="7" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="7" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="B11" s="7" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2626,10 +2621,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>194</v>
       </c>
     </row>
@@ -2674,19 +2669,19 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -2713,19 +2708,19 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>199</v>
+      <c r="B3" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2733,7 +2728,7 @@
         <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2768,10 +2763,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2780,7 +2775,7 @@
         <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2823,10 +2818,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>197</v>
       </c>
     </row>
@@ -2870,131 +2865,131 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="4" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3021,10 +3016,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3033,7 +3028,7 @@
         <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3057,7 +3052,7 @@
         <v>78</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3065,7 +3060,7 @@
         <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3077,50 +3072,50 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>214</v>
+      <c r="B10" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3156,10 +3151,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3168,7 +3163,7 @@
         <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3216,7 +3211,7 @@
         <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3224,7 +3219,7 @@
         <v>94</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3251,10 +3246,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>95</v>
       </c>
     </row>
@@ -3267,10 +3262,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3295,7 +3290,7 @@
         <v>100</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3303,7 +3298,7 @@
         <v>101</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3323,19 +3318,19 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>203</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -3344,18 +3339,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3576,18 +3571,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E254D28-D3D4-49BF-9139-FF4FDEF467DC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E21D230-F0FF-46F1-8C9B-DF853E5491B6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E21D230-F0FF-46F1-8C9B-DF853E5491B6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E254D28-D3D4-49BF-9139-FF4FDEF467DC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/src/test/resources/venueAddressValues.xlsx
+++ b/src/test/resources/venueAddressValues.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harpreet.jhita/IdeaProjects/ethos-repl-docmosis-service/src/test/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michael.brain/dev/ethos-repl-docmosis-service/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3879AAA2-555E-5346-84B1-6FDAE12D6441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E08E4B-1487-FC48-BB03-C6485E37546F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="1740" windowWidth="30940" windowHeight="16900" activeTab="2" xr2:uid="{57ECFE3E-99BE-FC40-B6CA-F6152164B97B}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="30240" windowHeight="16900" activeTab="6" xr2:uid="{57ECFE3E-99BE-FC40-B6CA-F6152164B97B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bristol" sheetId="3" r:id="rId1"/>
@@ -683,9 +683,6 @@
     <t>Leicester Hearing Centre, 5a New Walk, Leicester, LE1 6TE</t>
   </si>
   <si>
-    <t>Lincoln Magistrates Court, 358 High Street, Lincoln, LN5 7QA</t>
-  </si>
-  <si>
     <t>Boston Court House, 55 Norfolk Street, Boston, PE21 6PE</t>
   </si>
   <si>
@@ -955,6 +952,9 @@
   </si>
   <si>
     <t>7 Newgate Street, London, EC1A 7AZ</t>
+  </si>
+  <si>
+    <t>Lincoln County Court, 360 High Street, Lincoln LN5 7PS</t>
   </si>
 </sst>
 </file>
@@ -1740,18 +1740,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1772,10 +1772,10 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1788,122 +1788,122 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>249</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>239</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>241</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>243</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>247</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -1954,7 +1954,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1986,7 +1986,7 @@
         <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2002,7 +2002,7 @@
         <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2010,7 +2010,7 @@
         <v>113</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2034,7 +2034,7 @@
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2066,7 +2066,7 @@
         <v>120</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,7 +2154,7 @@
         <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2210,7 +2210,7 @@
         <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2226,7 +2226,7 @@
         <v>140</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2258,7 +2258,7 @@
         <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2314,7 @@
         <v>151</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2322,7 +2322,7 @@
         <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2330,7 +2330,7 @@
         <v>153</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2370,7 +2370,7 @@
         <v>158</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2386,7 +2386,7 @@
         <v>160</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2418,7 +2418,7 @@
         <v>164</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2426,7 +2426,7 @@
         <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>167</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2455,10 +2455,10 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -2490,7 +2490,7 @@
         <v>169</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2498,7 +2498,7 @@
         <v>170</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2506,7 +2506,7 @@
         <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2522,7 +2522,7 @@
         <v>89</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2530,7 +2530,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2538,7 +2538,7 @@
         <v>172</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
         <v>174</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2570,7 +2570,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2586,15 +2586,15 @@
         <v>177</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -2728,7 +2728,7 @@
         <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3028,7 +3028,7 @@
         <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3060,7 +3060,7 @@
         <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>215</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3163,7 +3163,7 @@
         <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3211,7 +3211,7 @@
         <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3219,7 +3219,7 @@
         <v>94</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3339,21 +3339,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E98ADB2028FC4F43824F86666CC83903" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff47f26d8558bca2ac2c896a7e751c25">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bc19a69a-bda7-4614-8881-f2ac618cff8e" xmlns:ns4="02128cc3-8226-4d54-9246-100bb62c9520" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="63ef4ea587d9ab0193671c85d2373b1f" ns3:_="" ns4:_="">
     <xsd:import namespace="bc19a69a-bda7-4614-8881-f2ac618cff8e"/>
@@ -3570,24 +3555,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E21D230-F0FF-46F1-8C9B-DF853E5491B6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E254D28-D3D4-49BF-9139-FF4FDEF467DC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00A2FE85-4E03-4320-929A-8E66617AF346}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3604,4 +3587,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E254D28-D3D4-49BF-9139-FF4FDEF467DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E21D230-F0FF-46F1-8C9B-DF853E5491B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>